--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_32.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_32.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Musician?</t>
+          <t>Sessions</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Diligence</t>
+          <t>Response</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.547509252243213</v>
+        <v>-0.2441749492407463</v>
       </c>
       <c r="C2">
-        <v>0.3186354034744374</v>
+        <v>-1.138423584289471</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.01274990838746317</v>
+        <v>2.31264198568679</v>
       </c>
       <c r="C3">
-        <v>1.839619975664474</v>
+        <v>0.8070106279184689</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.789870289614345</v>
+        <v>0.1125697483442623</v>
       </c>
       <c r="C4">
-        <v>1.007765720042719</v>
+        <v>-1.448050164630754</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.6096907034235725</v>
+        <v>0.489008461759854</v>
       </c>
       <c r="C5">
-        <v>0.06929279910922843</v>
+        <v>0.4171110901604813</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.1586959036299093</v>
+        <v>0.7073937318948923</v>
       </c>
       <c r="C6">
-        <v>0.8135476138172894</v>
+        <v>-0.3878069993260579</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.7599803386899965</v>
+        <v>-0.241703773937683</v>
       </c>
       <c r="C7">
-        <v>0.884854358154695</v>
+        <v>0.6826000823138783</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.4627186528809127</v>
+        <v>0.3432602821411838</v>
       </c>
       <c r="C8">
-        <v>1.137185838516828</v>
+        <v>-0.9420753348966687</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-2.133804324705214</v>
+        <v>1.206114962076824</v>
       </c>
       <c r="C9">
-        <v>-0.8146652263789665</v>
+        <v>-0.6195401554904143</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.4965554043345525</v>
+        <v>-0.5048527221338924</v>
       </c>
       <c r="C10">
-        <v>0.5671286875853848</v>
+        <v>0.2228048834052315</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.197318121610462</v>
+        <v>-2.093845681207473</v>
       </c>
       <c r="C11">
-        <v>0.1544282839335664</v>
+        <v>-0.9369961614308004</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.005472295348919</v>
+        <v>-0.8960899107311088</v>
       </c>
       <c r="C12">
-        <v>-1.539674328212656</v>
+        <v>-1.009661045185487</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-1.435799783872864</v>
+        <v>0.5254838116572268</v>
       </c>
       <c r="C13">
-        <v>-0.8974025650094354</v>
+        <v>-1.029626089201644</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.3083854204412489</v>
+        <v>-0.5500654077308539</v>
       </c>
       <c r="C14">
-        <v>0.4738109940237746</v>
+        <v>-0.2602028797110092</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.7333008283407111</v>
+        <v>-0.9913688019059202</v>
       </c>
       <c r="C15">
-        <v>-0.3218921247284859</v>
+        <v>-1.336756528823133</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.109629471324321</v>
+        <v>-0.375965447181383</v>
       </c>
       <c r="C16">
-        <v>-0.1237002423123035</v>
+        <v>-0.344082087672824</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.5820636941591264</v>
+        <v>0.8574371520548629</v>
       </c>
       <c r="C17">
-        <v>1.12101745224534</v>
+        <v>0.2836329207624809</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.5808556532212186</v>
+        <v>1.370312119179552</v>
       </c>
       <c r="C18">
-        <v>0.2054276310355563</v>
+        <v>1.163305196058285</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.03329838238517206</v>
+        <v>0.01997864508263682</v>
       </c>
       <c r="C19">
-        <v>-0.1343505099701244</v>
+        <v>0.4792698407030872</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.6369060530709809</v>
+        <v>-0.2605662510969163</v>
       </c>
       <c r="C20">
-        <v>0.3082863773998932</v>
+        <v>0.5360446984400623</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.3518239968732226</v>
+        <v>-0.4465360113948154</v>
       </c>
       <c r="C21">
-        <v>-0.6606159300662533</v>
+        <v>-1.543433757321985</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.4778279959905383</v>
+        <v>1.455752545027514</v>
       </c>
       <c r="C22">
-        <v>-0.2196085623319151</v>
+        <v>0.8131238633451608</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.3222412254217125</v>
+        <v>1.379375202639935</v>
       </c>
       <c r="C23">
-        <v>1.066705280406695</v>
+        <v>1.585863245423333</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.9764238107266086</v>
+        <v>-1.005255710308028</v>
       </c>
       <c r="C24">
-        <v>1.055047666097946</v>
+        <v>-0.6276966904363714</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-1.24100986622521</v>
+        <v>-0.1872184889430601</v>
       </c>
       <c r="C25">
-        <v>0.8148592578541051</v>
+        <v>-2.572508575792118</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.5541001488694761</v>
+        <v>-0.4071160429263173</v>
       </c>
       <c r="C26">
-        <v>-0.4115100302567549</v>
+        <v>1.340446163966888</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-2.071946777722204</v>
+        <v>0.6546157876653068</v>
       </c>
       <c r="C27">
-        <v>1.219891212914504</v>
+        <v>1.098400958868703</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.8102312030533826</v>
+        <v>-0.961105034997486</v>
       </c>
       <c r="C28">
-        <v>1.118119001115163</v>
+        <v>-0.8030856732555071</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.09088580810565329</v>
+        <v>1.055234863527454</v>
       </c>
       <c r="C29">
-        <v>-0.1520119687522184</v>
+        <v>1.620818344569573</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-1.088294974817886</v>
+        <v>0.2655624755827599</v>
       </c>
       <c r="C30">
-        <v>-0.6825329712915358</v>
+        <v>0.8527050669766628</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.03437805678384635</v>
+        <v>0.6721616255266869</v>
       </c>
       <c r="C31">
-        <v>-0.6373001681184228</v>
+        <v>-1.468591998910063</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>1.79785002650746</v>
+        <v>-2.304805802588589</v>
       </c>
       <c r="C32">
-        <v>0.06136631920613161</v>
+        <v>-0.6628531383743017</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.1679229262513522</v>
+        <v>0.9081407902004801</v>
       </c>
       <c r="C33">
-        <v>-0.912246995969086</v>
+        <v>0.6885680576859019</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-2.152556261127784</v>
+        <v>-0.02888775862638068</v>
       </c>
       <c r="C34">
-        <v>-0.7325599199161177</v>
+        <v>0.3245804242976196</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.1407198271468359</v>
+        <v>1.246787329592929</v>
       </c>
       <c r="C35">
-        <v>0.1421724990377203</v>
+        <v>0.9060339792939305</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.3277726232407054</v>
+        <v>-0.6836584883968561</v>
       </c>
       <c r="C36">
-        <v>-0.09159406836452265</v>
+        <v>-0.8571667285883215</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>1.282765816010053</v>
+        <v>1.74583897211002</v>
       </c>
       <c r="C37">
-        <v>-0.1510971215158071</v>
+        <v>-0.108570143065117</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>2.126482923940725</v>
+        <v>-2.885109698427836</v>
       </c>
       <c r="C38">
-        <v>0.4061034071541947</v>
+        <v>0.1485055129815935</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.0982629317250755</v>
+        <v>0.08276063983313056</v>
       </c>
       <c r="C39">
-        <v>-1.238435443989228</v>
+        <v>0.03814907050616537</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.6146128330441657</v>
+        <v>-0.656044094285711</v>
       </c>
       <c r="C40">
-        <v>0.8069576860891295</v>
+        <v>0.8494228982232197</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.7611974968503277</v>
+        <v>-0.545840181213601</v>
       </c>
       <c r="C41">
-        <v>0.1120001425196591</v>
+        <v>0.4069337438387242</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.006306545567684613</v>
+        <v>-0.3948885590957947</v>
       </c>
       <c r="C42">
-        <v>1.049475193769789</v>
+        <v>-0.5504140029190212</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>1.180260747751395</v>
+        <v>1.570291689629987</v>
       </c>
       <c r="C43">
-        <v>0.8467680738097387</v>
+        <v>0.5964894757969884</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.013380610356603</v>
+        <v>1.382818737349806</v>
       </c>
       <c r="C44">
-        <v>-0.573039886792045</v>
+        <v>-0.1272445244171611</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.1719035173224636</v>
+        <v>0.231147875127783</v>
       </c>
       <c r="C45">
-        <v>-2.294063170362853</v>
+        <v>0.335597121515633</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.8704306896927029</v>
+        <v>-0.8406977129610806</v>
       </c>
       <c r="C46">
-        <v>1.560200439361853</v>
+        <v>-0.3275344911019707</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.9732747490658985</v>
+        <v>-0.2483293575399418</v>
       </c>
       <c r="C47">
-        <v>-1.491140816468878</v>
+        <v>1.922502916337011</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.6477435910767817</v>
+        <v>0.1271621663861612</v>
       </c>
       <c r="C48">
-        <v>0.1497529634693445</v>
+        <v>-1.255032084591482</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.0917710820110894</v>
+        <v>-1.296443415788872</v>
       </c>
       <c r="C49">
-        <v>-0.08870015196552813</v>
+        <v>0.2111189427614316</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-1.324347260492059</v>
+        <v>-1.04876264077799</v>
       </c>
       <c r="C50">
-        <v>0.3208438176636602</v>
+        <v>-0.4840101696068958</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.597521105316308</v>
+        <v>-0.7860065232982973</v>
       </c>
       <c r="C51">
-        <v>0.1765402695470603</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>0.5141802954140162</v>
-      </c>
-      <c r="C52">
-        <v>0.4999586929959526</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>-1.69448173211355</v>
-      </c>
-      <c r="C53">
-        <v>1.190270775814652</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>-0.04734647651151372</v>
-      </c>
-      <c r="C54">
-        <v>-2.6098984364023</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>0.006928375873497564</v>
-      </c>
-      <c r="C55">
-        <v>0.0181127643341727</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>2.046504074622614</v>
-      </c>
-      <c r="C56">
-        <v>0.348050361922254</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>-0.4985442278570397</v>
-      </c>
-      <c r="C57">
-        <v>-2.734998942846434</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>1.493474459728757</v>
-      </c>
-      <c r="C58">
-        <v>0.9002274065392095</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>-2.899366801546504</v>
-      </c>
-      <c r="C59">
-        <v>0.7258068311508317</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>1.132023691299344</v>
-      </c>
-      <c r="C60">
-        <v>-0.06064706518346034</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>0.6713304106157867</v>
-      </c>
-      <c r="C61">
-        <v>-1.475721822003008</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>1.313848643798439</v>
-      </c>
-      <c r="C62">
-        <v>-0.3405190516706219</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>1.506385387729113</v>
-      </c>
-      <c r="C63">
-        <v>0.1479254988883802</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>1.261147303561656</v>
-      </c>
-      <c r="C64">
-        <v>0.4445566067607701</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>-0.3743861243904529</v>
-      </c>
-      <c r="C65">
-        <v>1.371063653035399</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>0.1043903635678154</v>
-      </c>
-      <c r="C66">
-        <v>-1.09085915804782</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>1.237033205230346</v>
-      </c>
-      <c r="C67">
-        <v>-2.928841938328818</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>-0.8088965225384516</v>
-      </c>
-      <c r="C68">
-        <v>-1.330774462013473</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>0.3673308319927673</v>
-      </c>
-      <c r="C69">
-        <v>-0.4350937958571308</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>1.544788448604209</v>
-      </c>
-      <c r="C70">
-        <v>-0.6166350081483066</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>0.8317454239135458</v>
-      </c>
-      <c r="C71">
-        <v>-0.4759114425506326</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>1.466650847227571</v>
-      </c>
-      <c r="C72">
-        <v>-1.265425912392034</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>0.426105107131563</v>
-      </c>
-      <c r="C73">
-        <v>0.07924764668940405</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>0.1490378707847939</v>
-      </c>
-      <c r="C74">
-        <v>0.5775175635154629</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>-0.71486384226496</v>
-      </c>
-      <c r="C75">
-        <v>1.521007656382154</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>-1.882752304835718</v>
-      </c>
-      <c r="C76">
-        <v>0.8408788887757025</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>-2.026380803594912</v>
-      </c>
-      <c r="C77">
-        <v>-0.09735095776728261</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>2.297758179464401</v>
-      </c>
-      <c r="C78">
-        <v>-2.264983840173413</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>0.08666691252787007</v>
-      </c>
-      <c r="C79">
-        <v>-0.5198814597201038</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>0.8668944261132425</v>
-      </c>
-      <c r="C80">
-        <v>0.3870553958967567</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>-0.9223424724790061</v>
-      </c>
-      <c r="C81">
-        <v>-1.175562947862612</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>-0.5894584014940406</v>
-      </c>
-      <c r="C82">
-        <v>-0.7048611197860605</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>1.245118034333521</v>
-      </c>
-      <c r="C83">
-        <v>0.1017605946368523</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>1.377339353839758</v>
-      </c>
-      <c r="C84">
-        <v>1.39103416663906</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>1.753658471821356</v>
-      </c>
-      <c r="C85">
-        <v>0.2051344643275157</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>0.8751222850487019</v>
-      </c>
-      <c r="C86">
-        <v>-0.1059058287671163</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>1.967105669307089</v>
-      </c>
-      <c r="C87">
-        <v>0.6923008844541938</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>-0.3109336090527103</v>
-      </c>
-      <c r="C88">
-        <v>-0.4455222595434319</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>-1.019098985094046</v>
-      </c>
-      <c r="C89">
-        <v>0.4079684887617916</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>-0.2753476648667968</v>
-      </c>
-      <c r="C90">
-        <v>-0.02883657477786232</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>-0.7098216420998261</v>
-      </c>
-      <c r="C91">
-        <v>0.2536500541065057</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>0.04779673425573708</v>
-      </c>
-      <c r="C92">
-        <v>0.9313320003112298</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>-0.3226560983122349</v>
-      </c>
-      <c r="C93">
-        <v>-1.661209795951928</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>-1.462768761192142</v>
-      </c>
-      <c r="C94">
-        <v>-0.1306551062757916</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>1.463941704178262</v>
-      </c>
-      <c r="C95">
-        <v>-0.765942463062517</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>0.906864162773163</v>
-      </c>
-      <c r="C96">
-        <v>-0.1140226749432795</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>-1.815677432880393</v>
-      </c>
-      <c r="C97">
-        <v>-0.9934508435639867</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>-1.561133536787436</v>
-      </c>
-      <c r="C98">
-        <v>-0.1267231027524205</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>0.6017897611932701</v>
-      </c>
-      <c r="C99">
-        <v>1.423004229811258</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>-1.587738371751167</v>
-      </c>
-      <c r="C100">
-        <v>-0.1569301908123695</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>1.017211029033455</v>
-      </c>
-      <c r="C101">
-        <v>-1.01637145027677</v>
+        <v>0.05454274182998337</v>
       </c>
     </row>
   </sheetData>
